--- a/result_docs/Dac_Ta_Y_Nghia_Cong_Thuc_Man_Hinh_Bao_Cao_PineDrama.xlsx
+++ b/result_docs/Dac_Ta_Y_Nghia_Cong_Thuc_Man_Hinh_Bao_Cao_PineDrama.xlsx
@@ -1807,7 +1807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" style="17" min="1" max="1"/>
@@ -1833,348 +1833,268 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>I. CÁC CHỈ SỐ HÀNH VI &amp; THỜI LƯỢNG TƯƠNG TÁC NGƯỜI DÙNG (3 THẺ KPI CHÍNH TRÊN UI MỚI)</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="34" customHeight="1" s="17">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Vị trí hiển thị trên màn hình</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Tên trường thông tin (Field Name)</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>Ví dụ hiển thị thực tế trên giao diện</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>Ý nghĩa của trường (Nghiệp vụ &amp; Người dùng)</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Công thức tính toán (Thuật ngữ người dùng / Logic nghiệp vụ)</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>Quy tắc nghiệp vụ &amp; Điều kiện áp dụng (Business Rules)</t>
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Thẻ thứ 1 (Bên trái) - Khối Báo Cáo Hành Vi &amp; Thời Lượng Tương Tác Người Dùng (Tab 2)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TỶ LỆ GIỮ CHÂN NGƯỜI DÙNG (Retention Rate)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>58.4% (▲ +4.2% so với kỳ trước)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Đo lường năng lực giữ chân khán giả của PineDrama trong kỳ báo cáo: Thể hiện tỷ lệ phần trăm người xem phim có hành vi quay trở lại mở ứng dụng và tiếp tục xem phim trong các ngày tiếp theo của kỳ lọc đã chọn.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1. Công thức chỉ số chính (%):
+Tỷ lệ giữ chân người dùng (%) = (Số lượng người dùng quay lại / Tổng số người dùng Active trong kỳ) × 100%
+• Mẫu số: Số Unique Users có ít nhất 1 phiên xem phim trong kỳ lọc.
+• Tử số: Số Unique Users có phát sinh xem phim ở ít nhất 2 ngày khác nhau trở lên trong kỳ lọc.
+* Trường hợp lọc 1 ngày (D-1): Áp dụng chuẩn D1 Retention: Tỷ lệ D1 (%) = (Số User mới ngày D0 mở lại app ngày D+1 / Tổng User mới ngày D0) × 100%
+2. Công thức biến động so với kỳ trước:
+Biến động (%) = Tỷ lệ giữ chân kỳ này (%) - Tỷ lệ giữ chân kỳ trước liền kề (%) (Điểm phần trăm)
+• Ví dụ: Kỳ này (10/08 - 20/08: 11 ngày) đạt 58.4%, kỳ liền kề trước đó đạt 54.2% -&gt; Biến động: +4.2%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>• Quy tắc màu sắc: Tỷ lệ &gt;= 50% hiển thị màu xanh lá neon #00e676 (Mức Tốt / Xuất sắc); 40% &lt;= Tỷ lệ &lt; 50% hiển thị màu vàng/cam (Trung bình); Tỷ lệ &lt; 40% hiển thị màu đỏ (Cảnh báo).
+• Quy tắc biến động: Tăng hiển thị icon ▲ dấu + màu xanh lá; Giảm hiển thị icon ▼ dấu - màu đỏ.
+• Điều kiện: Chốt số liệu sau khi kết thúc 23:59:59 của ngày cuối cùng trong kỳ. Làm tròn 1 chữ số thập phân (58.4%).</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="17">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>I. CÁC CHỈ SỐ GIỮ CHÂN NGƯỜI DÙNG THEO THỜI GIAN (USER RETENTION COHORT)</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="n"/>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="14" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Thẻ thứ 2 (Ở giữa) - Khối Báo Cáo Hành Vi &amp; Thời Lượng Tương Tác Người Dùng (Tab 2)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>THỜI GIAN XEM TRUNG BÌNH (Average Daily Watch Time)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>48.5 Phút / Ngày (▲ +6.5 phút so với kỳ trước)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Khắc họa mức độ nghiện phim và tiêu thụ nội dung hàng ngày của khán giả: Trung bình mỗi ngày một khán giả xem phim dành ra bao nhiêu phút trên PineDrama. Chỉ số này càng cao chứng tỏ khán giả có thói quen xem liên tục nhiều tập phim (cày phim - Binge-watching).</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1. Công thức chỉ số chính (Phút/Ngày):
+Thời gian xem TB (Phút/Ngày) = (Tổng số phút xem video của tất cả người dùng trong kỳ) / (Tổng số lượt User-Day hoạt động trong kỳ)
+• Tổng số phút xem: Tổng thời lượng phát video thực tế của tất cả khán giả trong kỳ (phút).
+• Tổng số lượt User-Day: Tổng cộng số ngày có xem phim của từng người dùng trong kỳ.
+• Ví dụ: Kỳ lọc 11 ngày có tổng 6,052,800 phút xem và 124,800 lượt User-Day -&gt; TB = 6,052,800 / 124,800 = 48.5 Phút/Ngày.
+2. Công thức biến động so với kỳ trước:
+Biến động (phút) = Thời gian xem TB kỳ này - Thời gian xem TB kỳ trước liền kề
+• Ví dụ: Kỳ này 48.5 phút/ngày, kỳ trước 42.0 phút/ngày -&gt; Biến động: +6.5 phút.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>• Chuẩn ngành phim ngắn: &gt;= 40 Phút/Ngày là mức Rất cao; 25 - 40 Phút/Ngày là Khá/Ổn định; &lt; 25 Phút/Ngày là Thấp.
+• Chống treo máy: Phiên xem liên tục không tương tác sau 3 giờ sẽ ngưng tính thời lượng từ phút 181 để tránh sai lệch do ngủ quên/treo máy.
+• Hiển thị: Làm tròn 1 chữ số thập phân, biến động hiển thị màu xanh dương neon #40c4ff.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="175.5" customHeight="1" s="17">
-      <c r="A6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Khối thẻ góc trái trên của Tab 2</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Thẻ thứ 3 (Bên phải) - Khối Báo Cáo Hành Vi &amp; Thời Lượng Tương Tác Người Dùng (Tab 2)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NGƯỜI DÙNG ACTIVE (Active Users in Period)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>124,800 Người (▲ +12.8% so với kỳ trước)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Đo lường quy mô khán giả thực tế tiếp cận và tiêu thụ nội dung trên nền tảng trong khoảng thời gian được lọc. Đây là chỉ số nền tảng quyết định độ lớn của thị phần người xem, sức sống ứng dụng và tiềm năng doanh thu.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1. Công thức chỉ số chính (Người):
+Người dùng Active = COUNT(DISTINCT user_id) trong kỳ lọc đã chọn
+• Điều kiện: Tài khoản hoặc thiết bị có sự kiện xem phim &gt;= 5 giây hoặc hoàn thành ít nhất 1 tập.
+• Khử trùng lặp: Mỗi người dùng chỉ tính 1 lần duy nhất trong toàn kỳ lọc dù xem phim ở nhiều ngày.
+2. Công thức tăng trưởng so với kỳ trước:
+Tăng trưởng (%) = [(Active kỳ này - Active kỳ trước) / Active kỳ trước] × 100%
+• Ví dụ: Kỳ này 124,800 người, kỳ trước 110,638 người -&gt; Tăng trưởng: +12.8%.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>• Tệp người dùng: Bao gồm cả User có tài khoản và Khách vãng lai (Guest qua Device ID).
+• Hiển thị: Định dạng có dấu phẩy phân cách hàng nghìn kèm chữ "Người" (124,800 Người).
+• Biến động: Tăng trưởng dương hiển thị icon ▲ dấu + màu xanh lá; Giảm hiển thị icon ▼ dấu - màu đỏ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="128" customHeight="1" s="17">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>II. CÁC CHỈ SỐ PHÂN TÍCH CHUYÊN SÂU (RETENTION COHORT CHI TIẾT - PHỤC VỤ DRILL-DOWN BÁO CÁO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="240" customHeight="1" s="17">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Phân tích Cohort chi tiết</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>D1 Retention (Quay lại sau 1 ngày)</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>58.4% (Tốt)</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Tỷ lệ người dùng mới cảm thấy thích thú với ứng dụng và quay lại mở app xem tiếp ngay vào ngày hôm sau (D+1).</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>1. Khi lọc 1 ngày (D-1): Tỷ lệ D1 (%) = (Số user trong nhóm D0 quay lại vào ngày D+1 / Tổng user mới nhóm D0) x 100%.
-• Ví dụ: Ngày 10/08 có 10,000 user mới, ngày 11/08 có 5,840 người mở lại app -&gt; D1 = 58.4%.
-2. Khi lọc KHOẢNG NGÀY (VD: 10/08 - 30/08, gồm 20 ngày): Là TRUNG BÌNH CÓ TRỌNG SỐ (không phải cộng tổng %):
-• D1 (Kỳ) = (Tổng User quay lại ngày D+1 của cả 20 nhóm / Tổng User mới của cả 20 nhóm) x 100%.
-• Ví dụ: Cả 20 ngày có 200,000 user mới, tổng số người quay lại D+1 của các ngày là 113,600 người -&gt; D1 trung bình = (113,600 / 200,000) x 100% = 56.8%.</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>• D1 chỉ chốt số trọn vẹn khi ngày hiện tại tối thiểu là ngày hôm sau của ngày cuối cùng trong kỳ lọc.
-• Chuẩn ngành phim ngắn: D1 &gt; 50% là mức xuất sắc (gắn nhãn xanh lá 'Tốt'). Dưới 40% là cảnh báo nội dung chưa đủ cuốn hút.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="128" customHeight="1" s="17">
-      <c r="A7" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Khối thẻ góc trái dưới của Tab 2</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>58.4%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Tỷ lệ người dùng mới có ấn tượng tích cực và quay lại mở app xem tiếp ngay vào ngày hôm sau (D+1).</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1. Lọc 1 ngày: Tỷ lệ D1 (%) = (Số user mới ngày D0 mở lại app ngày D+1 / Tổng user mới ngày D0) x 100%
+2. Lọc khoảng ngày: Trung bình có trọng số của các ngày đã hoàn thành chu kỳ D+1.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>• Chuẩn ngành phim ngắn: &gt;= 50% là Tốt/Xuất sắc; &lt; 40% là cảnh báo nội dung tập đầu chưa đủ cuốn hút. Chỉ chốt số liệu khi qua ngày D+1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="67.5" customHeight="1" s="17">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Phân tích Cohort chi tiết</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>D7 Retention (Quay lại sau 7 ngày)</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>34.8%</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>Đo lường thói quen xem phim hàng tuần của người dùng sau 7 ngày trải nghiệm (D+7).</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>1. Khi lọc 1 ngày: Tỷ lệ D7 (%) = (Số user trong nhóm D0 còn quay lại vào ngày thứ 7 / Tổng user mới nhóm D0) x 100%.
-2. Khi lọc KHOẢNG NGÀY: Là TRUNG BÌNH CÓ TRỌNG SỐ của các nhóm người dùng trong kỳ đã hoàn thành chu kỳ 7 ngày (D0 + 7 ngày).</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>• Chu kỳ 7 ngày trượt (Rolling 7 Days) tính từ ngày D0 cộng thêm 7 ngày.
-• Nếu ngày được chọn chưa trôi qua đủ 7 ngày so với hiện tại -&gt; Hiển thị dấu gạch ngang '--' (Chờ đủ 7 ngày), tuyệt đối không để 0%.
-• Mức chuẩn tốt của ứng dụng phim ngắn đạt từ 30% đến 40%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="240" customHeight="1" s="17">
-      <c r="A8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Khối thẻ góc phải trên của Tab 2</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Đo lường thói quen xem phim hàng tuần của khán giả mới sau 1 tuần trải nghiệm ứng dụng (D+7).</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1. Lọc 1 ngày: Tỷ lệ D7 (%) = (Số user mới ngày D0 còn quay lại ngày D+7 / Tổng user mới ngày D0) x 100%
+2. Lọc khoảng ngày: Trung bình có trọng số của các nhóm user đã đủ 7 ngày tuổi.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>• Chuẩn ngành: Đạt từ 30% đến 40% là Tốt. Những ngày chưa đủ 7 ngày tuổi không đưa vào mẫu số.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="17">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Phân tích Cohort chi tiết</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>D30 Retention (Quay lại sau 30 ngày)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>21.2%</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Tỷ lệ khán giả trung thành còn gắn bó với ứng dụng sau 1 tháng sử dụng (D+30). Đây là tệp người dùng cốt lõi mang lại giá trị vòng đời (LTV) lâu dài.</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
-        <is>
-          <t>1. BẢN CHẤT CHU KỲ 30 NGÀY (VẮT SANG THÁNG TIẾP THEO):
-• D30 là chu kỳ 30 ngày trượt tính từ ngày người dùng cài app (D0) VẮT SANG THÁNG TIẾP THEO (D0 + 30 ngày), KHÔNG PHẢI chỉ tính trong 30 ngày của cùng một tháng dương lịch:
-  + Khách vào ngày 05/08 -&gt; Mốc D30 chốt sổ vào ngày 04/09 (tháng sau).
-  + Khách vào ngày 15/08 -&gt; Mốc D30 chốt sổ vào ngày 14/09 (tháng sau).
-  + Khách vào ngày 30/08 -&gt; Mốc D30 chốt sổ vào ngày 29/09 (tháng sau).
-2. GIẢI THÍCH RÕ RÀNG KHI LỌC KHOẢNG NGÀY (VÍ DỤ: 10/08 - 30/08, DÀI 20 NGÀY):
-• Sự khác biệt giữa 2 khái niệm:
-  - Dải ngày lọc (10/08 - 30/08): Là KHOẢNG NGÀY SINH RA USER MỚI (ngày khách cài App D0).
-  - Chỉ số D30: Là số % user đó CÒN QUAY LẠI VÀO NGÀY THỨ 30 CỦA HỌ (rơi vào tháng 9).
-• Ví dụ minh họa thực tế khi mở màn hình xem báo cáo:
-  + Trường hợp 1: Nếu hôm nay là Tháng 10/2026 mở lọc kỳ 10/08 - 30/08: Vì thời gian thực tế đã qua tháng 9, toàn bộ user sinh ra từ 10/08 đến 30/08 ĐỀU ĐÃ SỐNG ĐỦ 30 NGÀY VÒNG ĐỜI (đã bước qua các ngày chốt sổ 09/09 -&gt; 29/09). Do đó hệ thống tính được D30 trọn vẹn cho cả nhóm!
-  + Công thức tính D30 cả kỳ là TRUNG BÌNH CÓ TRỌNG SỐ:
-    D30 cả kỳ = (Tổng user ngày D+30 còn vào App / Tổng user mới cả 20 ngày) × 100%
-    (Tuyệt đối KHÔNG PHẢI cộng dồn các con số % lại với nhau).
-  + Trường hợp 2: Nếu hôm nay là ngày 31/08/2026 (vừa hết kỳ lọc xem ngay): Trong đời thực chưa có user nào bước sang tháng 9 để đủ 30 ngày tuổi -&gt; Hiển thị '--' (Đang tích lũy chu kỳ).
-  + Trường hợp 3: Nếu hôm nay là ngày 20/09/2026: Khách từ 10/08-20/08 đã đủ 30 ngày; khách từ 21/08-30/08 chưa đủ -&gt; Hệ thống lấy trung bình D30 của những ngày đã đủ 30 ngày (kèm ghi chú *).</t>
-        </is>
-      </c>
-      <c r="G8" s="25" t="inlineStr">
-        <is>
-          <t>• QUY TẮC HIỂN THỊ KHI CHƯA ĐỦ 30 NGÀY:
-  + Tuyệt đối KHÔNG hiển thị '0%' hay lỗi 'NaN' khi chưa đủ thời gian kiểm chứng.
-  + Nếu chưa có ngày nào trong kỳ lọc đủ 30 ngày trôi qua (ví dụ lọc ngày hôm qua D-1, hoặc vừa hết tháng xem ngay) -&gt; Hiển thị dấu gạch ngang '--' (Đang tích lũy chu kỳ) với màu xám mờ.
-  + Nếu một phần ngày đã đủ 30 ngày, một phần chưa đủ (ví dụ đang ở giữa tháng 9 xem kỳ tháng 8) -&gt; Hệ thống tính trung bình D30 trên các nhóm ngày đã hoàn thành chu kỳ (kèm dấu hoa thị * giải thích).
-• Ý NGHĨA KINH DOANH: Chỉ số vàng đo lường độ trung thành và giá trị vòng đời (LTV) lâu dài của người dùng. Giữ chân D30 tốt mới quyết định hiệu quả khi mở rộng quy mô chạy marketing/quảng cáo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="67.5" customHeight="1" s="17">
-      <c r="A9" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Khối thẻ góc phải dưới của Tab 2</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Thời gian xem trung bình mỗi User</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>48.5 Phút / Ngày</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>Khắc họa mức độ nghiện phim của khán giả: Trung bình mỗi ngày một người dùng dành ra bao nhiêu phút để xem phim trên PineDrama.</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>Thời gian xem TB mỗi User = Tổng số phút xem video của tất cả người dùng trong ngày chia cho Tổng số người dùng hoạt động trong ngày.
-• Ví dụ: Tổng thời gian xem 6,052,800 phút / 124,800 Active Users = 48.5 phút/người/ngày.</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>Mức trung bình &gt; 40 phút/ngày chứng tỏ khán giả có thói quen xem liên tục nhiều tập phim (cày phim - Binge-watching).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="17">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>II. CÁC CHỈ SỐ PHÂN TÍCH HÀNH VI MỞ RỘNG (DÀNH CHO BÁO CÁO CHI TIẾT)</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11" ht="48" customHeight="1" s="17">
-      <c r="A11" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Chỉ số mở rộng quy mô</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Số người dùng hoạt động hàng ngày (DAU)</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>124,800 Users</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Quy mô lượng khán giả thực tế truy cập và sử dụng ứng dụng mỗi ngày.</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>Tổng số tài khoản hoặc thiết bị duy nhất có mở ứng dụng và phát sinh tương tác trong ngày.</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>Mỗi người dù mở app nhiều lần trong ngày thì cũng chỉ được tính là 1 DAU duy nhất.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1" s="17">
-      <c r="A12" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ số mở rộng tăng trưởng</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Số người dùng cài mới (New Users)</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>15,200 Người dùng mới</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Tốc độ thu hút khán giả mới cài đặt hoặc đăng ký tài khoản lần đầu trên nền tảng trong kỳ báo cáo.</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Tổng số thiết bị lần đầu cài đặt ứng dụng hoặc tài khoản mới tạo trong khoảng thời gian lọc.</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Loại trừ các trường hợp gỡ app rồi cài đặt lại trên cùng một thiết bị.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1" s="17">
-      <c r="A13" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Chỉ số mở rộng tương tác</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Số phiên mở app trung bình (Sessions per User)</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>3.8 Phiên / Ngày</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>Khán giả có thói quen mở ứng dụng bao nhiêu lần trong một ngày (các khung giờ rảnh như nghỉ trưa, đi xe bus, buổi tối).</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>Số phiên trung bình = Tổng số lần mở ứng dụng của tất cả người dùng / Tổng số người dùng hoạt động trong ngày.</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>Mỗi phiên được tính từ lúc mở app đến lúc tắt hoặc không tương tác quá 30 phút.</t>
-        </is>
-      </c>
-    </row>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Tỷ lệ khán giả trung thành cốt lõi còn gắn bó với ứng dụng sau 1 tháng sử dụng (D+30).</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1. Lọc 1 ngày: Tỷ lệ D30 (%) = (Số user mới ngày D0 mở lại app ngày D+30 / Tổng user mới ngày D0) x 100%
+2. Lọc khoảng ngày: Trung bình có trọng số của các nhóm user đã đủ 30 ngày tuổi.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>• Chuẩn ngành: &gt;= 20% là xuất sắc. Nếu chưa đủ 30 ngày hiển thị dấu gạch ngang "--" (Đang tích lũy chu kỳ), không để 0% hoặc NaN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="17"/>
+    <row r="12" ht="48" customHeight="1" s="17"/>
+    <row r="13" ht="48" customHeight="1" s="17"/>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result_docs/Dac_Ta_Y_Nghia_Cong_Thuc_Man_Hinh_Bao_Cao_PineDrama.xlsx
+++ b/result_docs/Dac_Ta_Y_Nghia_Cong_Thuc_Man_Hinh_Bao_Cao_PineDrama.xlsx
@@ -1807,7 +1807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" style="17" min="1" max="1"/>
@@ -1836,7 +1836,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. CÁC CHỈ SỐ HÀNH VI &amp; THỜI LƯỢNG TƯƠNG TÁC NGƯỜI DÙNG (3 THẺ KPI CHÍNH TRÊN UI MỚI)</t>
+          <t>BÁO CÁO HÀNH VI &amp; THỜI LƯỢNG TƯƠNG TÁC NGƯỜI DÙNG (2 THẺ CHỈ SỐ THEO UI MỚI)</t>
         </is>
       </c>
     </row>
@@ -1846,41 +1846,54 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thẻ thứ 1 (Bên trái) - Khối Báo Cáo Hành Vi &amp; Thời Lượng Tương Tác Người Dùng (Tab 2)</t>
+          <t>Thẻ thứ 1 (Bên trái)
+Khối Báo Cáo Hành Vi &amp; Thời Lượng Tương Tác Người Dùng (Tab 2)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TỶ LỆ GIỮ CHÂN NGƯỜI DÙNG (Retention Rate)</t>
+          <t>TỶ LỆ GIỮ CHÂN NGƯỜI DÙNG
+(Retention Rate)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>58.4% (▲ +4.2% so với kỳ trước)</t>
+          <t>58.4%
+▲ +4.2% so với kỳ trước
+(Phụ đề: Khán giả quay lại mở ứng dụng xem tiếp trong kỳ lọc đã chọn)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Đo lường năng lực giữ chân khán giả của PineDrama trong kỳ báo cáo: Thể hiện tỷ lệ phần trăm người xem phim có hành vi quay trở lại mở ứng dụng và tiếp tục xem phim trong các ngày tiếp theo của kỳ lọc đã chọn.</t>
+          <t>Đo lường năng lực giữ chân khán giả của PineDrama trong kỳ báo cáo: Thể hiện tỷ lệ phần trăm người xem phim có hành vi quay trở lại mở ứng dụng và tiếp tục xem phim trong các ngày tiếp theo của kỳ lọc đã chọn.
+Phản ánh trực tiếp độ hấp dẫn của nội dung, chất lượng kịch bản phim ngắn và hiệu quả giữ chân người xem.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>1. Công thức chỉ số chính (%):
 Tỷ lệ giữ chân người dùng (%) = (Số lượng người dùng quay lại / Tổng số người dùng Active trong kỳ) × 100%
-• Mẫu số: Số Unique Users có ít nhất 1 phiên xem phim trong kỳ lọc.
-• Tử số: Số Unique Users có phát sinh xem phim ở ít nhất 2 ngày khác nhau trở lên trong kỳ lọc.
-* Trường hợp lọc 1 ngày (D-1): Áp dụng chuẩn D1 Retention: Tỷ lệ D1 (%) = (Số User mới ngày D0 mở lại app ngày D+1 / Tổng User mới ngày D0) × 100%
+• Mẫu số (Tổng người dùng Active): Số Unique Users có ít nhất 1 phiên xem phim trong kỳ lọc.
+• Tử số (Số người dùng quay lại): Số Unique Users có phát sinh xem phim ở ít nhất 2 ngày khác nhau trở lên trong kỳ lọc đã chọn.
+* Trường hợp lọc 1 ngày (D-1): Tự động áp dụng chuẩn D1 Retention:
+Tỷ lệ D1 (%) = (Số User mới ngày D0 mở lại app ngày D+1 / Tổng User mới ngày D0) × 100%
 2. Công thức biến động so với kỳ trước:
 Biến động (%) = Tỷ lệ giữ chân kỳ này (%) - Tỷ lệ giữ chân kỳ trước liền kề (%) (Điểm phần trăm)
-• Ví dụ: Kỳ này (10/08 - 20/08: 11 ngày) đạt 58.4%, kỳ liền kề trước đó đạt 54.2% -&gt; Biến động: +4.2%</t>
+• Ví dụ: Kỳ này (10/08 - 20/08: 11 ngày) đạt 58.4%, kỳ liền kề trước đó (30/07 - 09/08: 11 ngày) đạt 54.2% ➔ Biến động: +4.2%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>• Quy tắc màu sắc: Tỷ lệ &gt;= 50% hiển thị màu xanh lá neon #00e676 (Mức Tốt / Xuất sắc); 40% &lt;= Tỷ lệ &lt; 50% hiển thị màu vàng/cam (Trung bình); Tỷ lệ &lt; 40% hiển thị màu đỏ (Cảnh báo).
-• Quy tắc biến động: Tăng hiển thị icon ▲ dấu + màu xanh lá; Giảm hiển thị icon ▼ dấu - màu đỏ.
-• Điều kiện: Chốt số liệu sau khi kết thúc 23:59:59 của ngày cuối cùng trong kỳ. Làm tròn 1 chữ số thập phân (58.4%).</t>
+          <t>• Quy tắc màu sắc ngưỡng đánh giá:
+  - Tỷ lệ ≥ 50%: Màu xanh lá neon #00e676 (Mức Tốt / Xuất sắc).
+  - 40% ≤ Tỷ lệ &lt; 50%: Màu vàng/cam #ffb300 (Mức Trung bình).
+  - Tỷ lệ &lt; 40%: Màu đỏ #ff5252 (Mức Cảnh báo rời bỏ cao).
+• Quy tắc hiển thị biến động:
+  - Tăng: Icon ▲ kèm dấu + và giá trị, màu xanh lá.
+  - Giảm: Icon ▼ kèm dấu - và giá trị, màu đỏ.
+  - Bằng nhau: 0.0% so với kỳ trước, màu xám.
+• Điều kiện chốt số liệu: Dữ liệu giữ chân người dùng chỉ chốt số trọn vẹn sau khi kết thúc 23:59:59 của ngày cuối cùng trong kỳ lọc.
+• Làm tròn: Làm tròn 1 chữ số thập phân (Ví dụ: 58.4%).</t>
         </is>
       </c>
     </row>
@@ -1890,210 +1903,66 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thẻ thứ 2 (Ở giữa) - Khối Báo Cáo Hành Vi &amp; Thời Lượng Tương Tác Người Dùng (Tab 2)</t>
+          <t>Thẻ thứ 2 (Bên phải)
+Khối Báo Cáo Hành Vi &amp; Thời Lượng Tương Tác Người Dùng (Tab 2)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>THỜI GIAN XEM TRUNG BÌNH (Average Daily Watch Time)</t>
+          <t>THỜI GIAN XEM TRUNG BÌNH
+(Average Daily Watch Time)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>48.5 Phút / Ngày (▲ +6.5 phút so với kỳ trước)</t>
+          <t>48.5 Phút / Ngày
+▲ +6.5 phút so với kỳ trước
+(Phụ đề: Thời lượng bình quân mỗi khán giả xem mỗi ngày trong kỳ)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Khắc họa mức độ nghiện phim và tiêu thụ nội dung hàng ngày của khán giả: Trung bình mỗi ngày một khán giả xem phim dành ra bao nhiêu phút trên PineDrama. Chỉ số này càng cao chứng tỏ khán giả có thói quen xem liên tục nhiều tập phim (cày phim - Binge-watching).</t>
+          <t>Khắc họa mức độ "nghiện phim" và tiêu thụ nội dung hàng ngày của khán giả: Trung bình mỗi ngày một khán giả xem phim dành ra bao nhiêu phút trên PineDrama.
+Chỉ số này càng cao chứng tỏ người xem có thói quen xem liên tục nhiều tập phim (cày phim - Binge-watching), mức độ gắn bó với ứng dụng rất sâu.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>1. Công thức chỉ số chính (Phút/Ngày):
 Thời gian xem TB (Phút/Ngày) = (Tổng số phút xem video của tất cả người dùng trong kỳ) / (Tổng số lượt User-Day hoạt động trong kỳ)
-• Tổng số phút xem: Tổng thời lượng phát video thực tế của tất cả khán giả trong kỳ (phút).
-• Tổng số lượt User-Day: Tổng cộng số ngày có xem phim của từng người dùng trong kỳ.
-• Ví dụ: Kỳ lọc 11 ngày có tổng 6,052,800 phút xem và 124,800 lượt User-Day -&gt; TB = 6,052,800 / 124,800 = 48.5 Phút/Ngày.
+• Tổng số phút xem: Tổng thời lượng phát video thực tế của tất cả khán giả trong kỳ (quy đổi ra phút).
+• Tổng số lượt User-Day: Tổng cộng số ngày có xem phim của từng người dùng trong kỳ (Mỗi User xem trong 1 ngày = 1 User-Day).
+• Ví dụ: Trong kỳ lọc 11 ngày, hệ thống ghi nhận tổng 6,052,800 phút xem phim qua 124,800 lượt User-Day ➔ Thời gian xem TB = 6,052,800 / 124,800 = 48.5 Phút/Ngày.
 2. Công thức biến động so với kỳ trước:
 Biến động (phút) = Thời gian xem TB kỳ này - Thời gian xem TB kỳ trước liền kề
-• Ví dụ: Kỳ này 48.5 phút/ngày, kỳ trước 42.0 phút/ngày -&gt; Biến động: +6.5 phút.</t>
+• Ví dụ: Kỳ này 48.5 phút/ngày, kỳ trước 42.0 phút/ngày ➔ Biến động: +6.5 phút.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>• Chuẩn ngành phim ngắn: &gt;= 40 Phút/Ngày là mức Rất cao; 25 - 40 Phút/Ngày là Khá/Ổn định; &lt; 25 Phút/Ngày là Thấp.
-• Chống treo máy: Phiên xem liên tục không tương tác sau 3 giờ sẽ ngưng tính thời lượng từ phút 181 để tránh sai lệch do ngủ quên/treo máy.
-• Hiển thị: Làm tròn 1 chữ số thập phân, biến động hiển thị màu xanh dương neon #40c4ff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="175.5" customHeight="1" s="17">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Thẻ thứ 3 (Bên phải) - Khối Báo Cáo Hành Vi &amp; Thời Lượng Tương Tác Người Dùng (Tab 2)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>NGƯỜI DÙNG ACTIVE (Active Users in Period)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>124,800 Người (▲ +12.8% so với kỳ trước)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Đo lường quy mô khán giả thực tế tiếp cận và tiêu thụ nội dung trên nền tảng trong khoảng thời gian được lọc. Đây là chỉ số nền tảng quyết định độ lớn của thị phần người xem, sức sống ứng dụng và tiềm năng doanh thu.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1. Công thức chỉ số chính (Người):
-Người dùng Active = COUNT(DISTINCT user_id) trong kỳ lọc đã chọn
-• Điều kiện: Tài khoản hoặc thiết bị có sự kiện xem phim &gt;= 5 giây hoặc hoàn thành ít nhất 1 tập.
-• Khử trùng lặp: Mỗi người dùng chỉ tính 1 lần duy nhất trong toàn kỳ lọc dù xem phim ở nhiều ngày.
-2. Công thức tăng trưởng so với kỳ trước:
-Tăng trưởng (%) = [(Active kỳ này - Active kỳ trước) / Active kỳ trước] × 100%
-• Ví dụ: Kỳ này 124,800 người, kỳ trước 110,638 người -&gt; Tăng trưởng: +12.8%.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>• Tệp người dùng: Bao gồm cả User có tài khoản và Khách vãng lai (Guest qua Device ID).
-• Hiển thị: Định dạng có dấu phẩy phân cách hàng nghìn kèm chữ "Người" (124,800 Người).
-• Biến động: Tăng trưởng dương hiển thị icon ▲ dấu + màu xanh lá; Giảm hiển thị icon ▼ dấu - màu đỏ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="128" customHeight="1" s="17">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>II. CÁC CHỈ SỐ PHÂN TÍCH CHUYÊN SÂU (RETENTION COHORT CHI TIẾT - PHỤC VỤ DRILL-DOWN BÁO CÁO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="240" customHeight="1" s="17">
-      <c r="A8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Phân tích Cohort chi tiết</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>D1 Retention (Quay lại sau 1 ngày)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>58.4%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Tỷ lệ người dùng mới có ấn tượng tích cực và quay lại mở app xem tiếp ngay vào ngày hôm sau (D+1).</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1. Lọc 1 ngày: Tỷ lệ D1 (%) = (Số user mới ngày D0 mở lại app ngày D+1 / Tổng user mới ngày D0) x 100%
-2. Lọc khoảng ngày: Trung bình có trọng số của các ngày đã hoàn thành chu kỳ D+1.</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>• Chuẩn ngành phim ngắn: &gt;= 50% là Tốt/Xuất sắc; &lt; 40% là cảnh báo nội dung tập đầu chưa đủ cuốn hút. Chỉ chốt số liệu khi qua ngày D+1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="67.5" customHeight="1" s="17">
-      <c r="A9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Phân tích Cohort chi tiết</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>D7 Retention (Quay lại sau 7 ngày)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>34.8%</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Đo lường thói quen xem phim hàng tuần của khán giả mới sau 1 tuần trải nghiệm ứng dụng (D+7).</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1. Lọc 1 ngày: Tỷ lệ D7 (%) = (Số user mới ngày D0 còn quay lại ngày D+7 / Tổng user mới ngày D0) x 100%
-2. Lọc khoảng ngày: Trung bình có trọng số của các nhóm user đã đủ 7 ngày tuổi.</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>• Chuẩn ngành: Đạt từ 30% đến 40% là Tốt. Những ngày chưa đủ 7 ngày tuổi không đưa vào mẫu số.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="17">
-      <c r="A10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Phân tích Cohort chi tiết</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>D30 Retention (Quay lại sau 30 ngày)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>21.2%</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Tỷ lệ khán giả trung thành cốt lõi còn gắn bó với ứng dụng sau 1 tháng sử dụng (D+30).</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1. Lọc 1 ngày: Tỷ lệ D30 (%) = (Số user mới ngày D0 mở lại app ngày D+30 / Tổng user mới ngày D0) x 100%
-2. Lọc khoảng ngày: Trung bình có trọng số của các nhóm user đã đủ 30 ngày tuổi.</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>• Chuẩn ngành: &gt;= 20% là xuất sắc. Nếu chưa đủ 30 ngày hiển thị dấu gạch ngang "--" (Đang tích lũy chu kỳ), không để 0% hoặc NaN.</t>
-        </is>
-      </c>
-    </row>
+          <t>• Chuẩn đánh giá ngành phim ngắn:
+  - ≥ 40 Phút/Ngày: Mức Rất cao (khán giả xem từ 30 - 50 tập phim ngắn/ngày).
+  - Từ 25 đến dưới 40 Phút/Ngày: Mức Khá / Ổn định.
+  - Dưới 25 Phút/Ngày: Mức Thấp (cần tối ưu chất lượng mở đầu tập 1-3 và nút bấm tự chuyển tập tiếp theo).
+• Quy tắc lọc dữ liệu rác (Anti-Bot &amp; Chống treo máy):
+  - Một phiên xem video liên tục không có thao tác tương tác sau 3 giờ sẽ tạm ngưng tính thời lượng từ phút thứ 181 để tránh sai lệch dữ liệu do ngủ quên hoặc treo máy.
+• Quy tắc hiển thị: Làm tròn 1 chữ số thập phân kèm đơn vị "Phút / Ngày", chỉ số biến động hiển thị màu xanh dương neon #40c4ff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="175.5" customHeight="1" s="17"/>
+    <row r="7" ht="128" customHeight="1" s="17"/>
+    <row r="8" ht="240" customHeight="1" s="17"/>
+    <row r="9" ht="67.5" customHeight="1" s="17"/>
+    <row r="10" ht="16.5" customHeight="1" s="17"/>
     <row r="11" ht="48" customHeight="1" s="17"/>
     <row r="12" ht="48" customHeight="1" s="17"/>
     <row r="13" ht="48" customHeight="1" s="17"/>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/result_docs/Dac_Ta_Y_Nghia_Cong_Thuc_Man_Hinh_Bao_Cao_PineDrama.xlsx
+++ b/result_docs/Dac_Ta_Y_Nghia_Cong_Thuc_Man_Hinh_Bao_Cao_PineDrama.xlsx
@@ -1871,15 +1871,30 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1. Công thức chỉ số chính (%):
+          <t>1. CÔNG THỨC CHỈ SỐ CHÍNH (%):
 Tỷ lệ giữ chân người dùng (%) = (Số lượng người dùng quay lại / Tổng số người dùng Active trong kỳ) × 100%
 • Mẫu số (Tổng người dùng Active): Số Unique Users có ít nhất 1 phiên xem phim trong kỳ lọc.
 • Tử số (Số người dùng quay lại): Số Unique Users có phát sinh xem phim ở ít nhất 2 ngày khác nhau trở lên trong kỳ lọc đã chọn.
-* Trường hợp lọc 1 ngày (D-1): Tự động áp dụng chuẩn D1 Retention:
+────────────────────────────────────────
+► VÍ DỤ 1: KHI LỌC KHOẢNG NGÀY (VD: Kỳ lọc 11 ngày từ 10/08 đến 20/08):
+- Mẫu số: Toàn bộ 11 ngày có 100,000 khán giả duy nhất (Unique Users) có mở xem phim.
+- Tử số: Trong 100,000 khán giả đó, có 58,400 người có xem phim ở từ 2 ngày khác nhau trở lên trong kỳ (VD: xem ngày 10/08 và quay lại xem tiếp ngày 12/08...).
+➔ Tỷ lệ giữ chân = (58,400 / 100,000) × 100% = 58.4%.
+(41,600 người còn lại chỉ vào xem 1 ngày duy nhất rồi chưa quay lại).
+────────────────────────────────────────
+► VÍ DỤ 2: KHI LỌC 1 NGÀY (D-1 mặc định, VD: Ngày 10/08):
+Tự động áp dụng chuẩn D1 Retention Cohort (Giữ chân sau 24h):
 Tỷ lệ D1 (%) = (Số User mới ngày D0 mở lại app ngày D+1 / Tổng User mới ngày D0) × 100%
-2. Công thức biến động so với kỳ trước:
-Biến động (%) = Tỷ lệ giữ chân kỳ này (%) - Tỷ lệ giữ chân kỳ trước liền kề (%) (Điểm phần trăm)
-• Ví dụ: Kỳ này (10/08 - 20/08: 11 ngày) đạt 58.4%, kỳ liền kề trước đó (30/07 - 09/08: 11 ngày) đạt 54.2% ➔ Biến động: +4.2%</t>
+- Mẫu số: Ngày 10/08 (D0) có 10,000 người dùng mới cài app &amp; xem phim lần đầu.
+- Tử số: Sang ngày 11/08 (D+1), có 5,840 người trong nhóm đó quay lại mở app xem tiếp.
+➔ Tỷ lệ D1 = (5,840 / 10,000) × 100% = 58.4%.
+────────────────────────────────────────
+2. CÔNG THỨC BIẾN ĐỘNG SO VỚI KỲ TRƯỚC:
+Biến động (%) = Tỷ lệ giữ chân kỳ này (%) - Tỷ lệ giữ chân kỳ trước liền kề (%)
+► VÍ DỤ 3: TÍNH BIẾN ĐỘNG:
+- Kỳ này (10/08 - 20/08: 11 ngày): Đạt 58.4%.
+- Kỳ trước liền kề (30/07 - 09/08: cùng 11 ngày): Đạt 54.2%.
+➔ Biến động = 58.4% - 54.2% = +4.2% (Hiển thị icon ▲ +4.2% so với kỳ trước).</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1928,14 +1943,21 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1. Công thức chỉ số chính (Phút/Ngày):
+          <t>1. CÔNG THỨC CHỈ SỐ CHÍNH (Phút/Ngày):
 Thời gian xem TB (Phút/Ngày) = (Tổng số phút xem video của tất cả người dùng trong kỳ) / (Tổng số lượt User-Day hoạt động trong kỳ)
 • Tổng số phút xem: Tổng thời lượng phát video thực tế của tất cả khán giả trong kỳ (quy đổi ra phút).
 • Tổng số lượt User-Day: Tổng cộng số ngày có xem phim của từng người dùng trong kỳ (Mỗi User xem trong 1 ngày = 1 User-Day).
-• Ví dụ: Trong kỳ lọc 11 ngày, hệ thống ghi nhận tổng 6,052,800 phút xem phim qua 124,800 lượt User-Day ➔ Thời gian xem TB = 6,052,800 / 124,800 = 48.5 Phút/Ngày.
-2. Công thức biến động so với kỳ trước:
+────────────────────────────────────────
+► VÍ DỤ MINH HỌA:
+- Trong kỳ lọc 11 ngày (10/08 - 20/08), hệ thống ghi nhận:
+  + Tổng số phút xem phim tích lũy toàn hệ thống = 6,052,800 phút.
+  + Tổng số lượt khán giả hoạt động (User-Day) = 124,800 lượt.
+➔ Thời gian xem TB = 6,052,800 / 124,800 = 48.5 Phút / Ngày.
+────────────────────────────────────────
+2. CÔNG THỨC BIẾN ĐỘNG SO VỚI KỲ TRƯỚC:
 Biến động (phút) = Thời gian xem TB kỳ này - Thời gian xem TB kỳ trước liền kề
-• Ví dụ: Kỳ này 48.5 phút/ngày, kỳ trước 42.0 phút/ngày ➔ Biến động: +6.5 phút.</t>
+- Kỳ này đạt 48.5 phút/ngày; kỳ trước liền kề đạt 42.0 phút/ngày.
+➔ Biến động = 48.5 - 42.0 = +6.5 phút (Hiển thị icon ▲ +6.5 phút so với kỳ trước).</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1960,10 +1982,10 @@
     <row r="13" ht="48" customHeight="1" s="17"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result_docs/Dac_Ta_Y_Nghia_Cong_Thuc_Man_Hinh_Bao_Cao_PineDrama.xlsx
+++ b/result_docs/Dac_Ta_Y_Nghia_Cong_Thuc_Man_Hinh_Bao_Cao_PineDrama.xlsx
@@ -1873,25 +1873,27 @@
         <is>
           <t>1. CÔNG THỨC CHỈ SỐ CHÍNH (%):
 Tỷ lệ giữ chân người dùng (%) = (Số lượng người dùng quay lại / Tổng số người dùng Active trong kỳ) × 100%
-• Mẫu số (Tổng người dùng Active): Số Unique Users có ít nhất 1 phiên xem phim trong kỳ lọc.
-• Tử số (Số người dùng quay lại): Số Unique Users có phát sinh xem phim ở ít nhất 2 ngày khác nhau trở lên trong kỳ lọc đã chọn.
 ────────────────────────────────────────
-► VÍ DỤ 1: KHI LỌC KHOẢNG NGÀY (VD: Kỳ lọc 11 ngày từ 10/08 đến 20/08):
-- Mẫu số: Toàn bộ 11 ngày có 100,000 khán giả duy nhất (Unique Users) có mở xem phim.
-- Tử số: Trong 100,000 khán giả đó, có 58,400 người có xem phim ở từ 2 ngày khác nhau trở lên trong kỳ (VD: xem ngày 10/08 và quay lại xem tiếp ngày 12/08...).
-➔ Tỷ lệ giữ chân = (58,400 / 100,000) × 100% = 58.4%.
-(41,600 người còn lại chỉ vào xem 1 ngày duy nhất rồi chưa quay lại).
+► TRƯỜNG HỢP 1: KHI LỌC 1 NGÀY (VD: Lọc ngày 10/08)
+Áp dụng chuẩn D1 Retention (Đo lường năng lực kéo người dùng hôm qua quay lại hôm nay):
+• Mẫu số: Tổng số người dùng mới cài app &amp; xem phim vào ngày hôm trước (Ngày 09/08).
+• Tử số: Số người dùng mới của ngày 09/08 có quay lại mở app xem tiếp vào chính ngày đang lọc (Ngày 10/08).
+Ví dụ minh họa:
+- Ngày hôm trước (09/08): Hệ thống đón 10,000 người dùng mới (Mẫu số = 10,000).
+- Ngày đang lọc (10/08): Trong 10,000 người đó, có 5,840 người quay lại mở app xem tiếp (Tử số = 5,840).
+➔ Tỷ lệ D1 ngày 10/08 = (5,840 / 10,000) × 100% = 58.4%.
+* Ưu điểm nghiệp vụ: Số liệu chốt ngay trong ngày 10/08, người xem filter ngày 10/08 là có ngay số liệu thực tế mà không cần đợi sang ngày 11/08!
 ────────────────────────────────────────
-► VÍ DỤ 2: KHI LỌC 1 NGÀY (D-1 mặc định, VD: Ngày 10/08):
-Tự động áp dụng chuẩn D1 Retention Cohort (Giữ chân sau 24h):
-Tỷ lệ D1 (%) = (Số User mới ngày D0 mở lại app ngày D+1 / Tổng User mới ngày D0) × 100%
-- Mẫu số: Ngày 10/08 (D0) có 10,000 người dùng mới cài app &amp; xem phim lần đầu.
-- Tử số: Sang ngày 11/08 (D+1), có 5,840 người trong nhóm đó quay lại mở app xem tiếp.
-➔ Tỷ lệ D1 = (5,840 / 10,000) × 100% = 58.4%.
+► TRƯỜNG HỢP 2: KHI LỌC KHOẢNG NGÀY (VD: Kỳ lọc 11 ngày từ 10/08 đến 20/08)
+Tỷ lệ giữ chân trong kỳ (%) = (Số Unique Users quay lại / Tổng Unique Users Active trong kỳ) × 100%
+- Mẫu số (Tổng Active trong kỳ): Toàn bộ 11 ngày có 100,000 khán giả duy nhất (Unique Users) có mở xem phim.
+- Tử số (Số người quay lại): Trong 100,000 khán giả đó, có 58,400 người có xem phim ở từ 2 ngày khác nhau trở lên trong kỳ (VD: xem ngày 10/08 và xem tiếp ngày 12/08...).
+➔ Tỷ lệ giữ chân cả kỳ = (58,400 / 100,000) × 100% = 58.4%.
+(41,600 người còn lại chỉ vào xem 1 ngày duy nhất trong cả kỳ lọc rồi chưa quay lại).
 ────────────────────────────────────────
 2. CÔNG THỨC BIẾN ĐỘNG SO VỚI KỲ TRƯỚC:
 Biến động (%) = Tỷ lệ giữ chân kỳ này (%) - Tỷ lệ giữ chân kỳ trước liền kề (%)
-► VÍ DỤ 3: TÍNH BIẾN ĐỘNG:
+► Ví dụ:
 - Kỳ này (10/08 - 20/08: 11 ngày): Đạt 58.4%.
 - Kỳ trước liền kề (30/07 - 09/08: cùng 11 ngày): Đạt 54.2%.
 ➔ Biến động = 58.4% - 54.2% = +4.2% (Hiển thị icon ▲ +4.2% so với kỳ trước).</t>
@@ -1907,7 +1909,9 @@
   - Tăng: Icon ▲ kèm dấu + và giá trị, màu xanh lá.
   - Giảm: Icon ▼ kèm dấu - và giá trị, màu đỏ.
   - Bằng nhau: 0.0% so với kỳ trước, màu xám.
-• Điều kiện chốt số liệu: Dữ liệu giữ chân người dùng chỉ chốt số trọn vẹn sau khi kết thúc 23:59:59 của ngày cuối cùng trong kỳ lọc.
+• Điều kiện chốt số liệu:
+  - Khi lọc 1 ngày (10/08): Số liệu D1 được chốt hoàn tất vào cuối ngày 10/08 (23:59:59).
+  - Khi lọc khoảng ngày: Dữ liệu chốt sau khi kết thúc ngày cuối cùng của kỳ lọc.
 • Làm tròn: Làm tròn 1 chữ số thập phân (Ví dụ: 58.4%).</t>
         </is>
       </c>
@@ -1982,10 +1986,10 @@
     <row r="13" ht="48" customHeight="1" s="17"/>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
